--- a/4.5.2 интерференция лазерного излучения/измерения.xlsx
+++ b/4.5.2 интерференция лазерного излучения/измерения.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="15850" windowHeight="7260" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15850" windowHeight="7260" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="поляризация" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="12">
   <si>
     <t>h1</t>
   </si>
@@ -59,6 +59,9 @@
   </si>
   <si>
     <t>x, cm</t>
+  </si>
+  <si>
+    <t>V3</t>
   </si>
 </sst>
 </file>
@@ -295,6 +298,162 @@
           </c:yVal>
           <c:smooth val="0"/>
         </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>cos</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>поляризация!$L$2:$L$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4.6326794879957784E-5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.7199329254596517E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.17368873128572007</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.25885633511600636</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.34205400206265668</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.42264858496828306</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.50002674654903656</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.57359962698652556</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.6428073252424229</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.7071231599922605</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.76605767775204758</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.81916237769524569</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.86603312481366335</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.90631322544758852</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.9396961417798968</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.98480864683955149</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.17359748522936377</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>поляризация!$I$2:$I$19</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="18"/>
+                <c:pt idx="0">
+                  <c:v>0.84119102419205982</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>5.0507627227610548E-2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>8.5777754279601548E-2</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.18200549450549455</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.32991443953692906</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.37500000000000006</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.39516790469763929</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.48014537720098571</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>0.65860697374223975</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>0.71004694680469305</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>0.80943644042863794</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>0.82480200891454247</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>0.83333333333333326</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>0.82915801515453269</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>0.90750110018012831</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>0.88262807545704525</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>0.87778772836950714</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>0.21023959382255281</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+        </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
           <c:showVal val="0"/>
@@ -303,11 +462,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="318505176"/>
-        <c:axId val="318504784"/>
+        <c:axId val="426845232"/>
+        <c:axId val="426846016"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="318505176"/>
+        <c:axId val="426845232"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -364,12 +523,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="318504784"/>
+        <c:crossAx val="426846016"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="318504784"/>
+        <c:axId val="426846016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -426,7 +585,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="318505176"/>
+        <c:crossAx val="426845232"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -729,11 +888,11 @@
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
         </c:dLbls>
-        <c:axId val="318501256"/>
-        <c:axId val="318500080"/>
+        <c:axId val="426851112"/>
+        <c:axId val="426850328"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="318501256"/>
+        <c:axId val="426851112"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -790,12 +949,12 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="318500080"/>
+        <c:crossAx val="426850328"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="318500080"/>
+        <c:axId val="426850328"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -852,7 +1011,7 @@
             <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="318501256"/>
+        <c:crossAx val="426851112"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2017,16 +2176,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>12700</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>501650</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>317500</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>196850</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2052,16 +2211,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>393700</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>590550</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>177800</xdr:rowOff>
+      <xdr:rowOff>139700</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>88900</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
+      <xdr:rowOff>120650</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2346,13 +2505,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:L25"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>8</v>
       </c>
@@ -2378,13 +2537,13 @@
         <v>6</v>
       </c>
       <c r="I1" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>0</v>
       </c>
@@ -2423,8 +2582,12 @@
         <f>COS(A2/180 * 3.1415)*COS(A2/180 * 3.1415)</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L2">
+        <f>COS(A2/180 * 3.1415)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>90</v>
       </c>
@@ -2460,11 +2623,15 @@
         <v>1</v>
       </c>
       <c r="K3">
-        <f t="shared" ref="K3:K19" si="4">COS(A3/180 * 3.1415)*COS(A3/180 * 3.1415)</f>
+        <f t="shared" ref="K3:K20" si="4">COS(A3/180 * 3.1415)*COS(A3/180 * 3.1415)</f>
         <v>2.1461719238496826E-9</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L3">
+        <f t="shared" ref="L3:L20" si="5">COS(A3/180 * 3.1415)</f>
+        <v>4.6326794879957784E-5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>85</v>
       </c>
@@ -2503,8 +2670,12 @@
         <f t="shared" si="4"/>
         <v>7.6037230224515317E-3</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L4">
+        <f t="shared" si="5"/>
+        <v>8.7199329254596517E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>80</v>
       </c>
@@ -2543,8 +2714,12 @@
         <f t="shared" si="4"/>
         <v>3.0167775375643073E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L5">
+        <f t="shared" si="5"/>
+        <v>0.17368873128572007</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>75</v>
       </c>
@@ -2583,8 +2758,12 @@
         <f t="shared" si="4"/>
         <v>6.7006602229690196E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L6">
+        <f t="shared" si="5"/>
+        <v>0.25885633511600636</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>70</v>
       </c>
@@ -2624,8 +2803,12 @@
         <f t="shared" si="4"/>
         <v>0.11700094032707994</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L7">
+        <f t="shared" si="5"/>
+        <v>0.34205400206265668</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>65</v>
       </c>
@@ -2642,27 +2825,31 @@
         <v>29.5</v>
       </c>
       <c r="F8">
-        <f t="shared" ref="F8:F18" si="5">B8/C8</f>
+        <f t="shared" ref="F8:F18" si="6">B8/C8</f>
         <v>0.10212765957446808</v>
       </c>
       <c r="G8">
-        <f t="shared" ref="G8:G18" si="6">(E8-D8)/(E8+D8)</f>
+        <f t="shared" ref="G8:G18" si="7">(E8-D8)/(E8+D8)</f>
         <v>0.22916666666666666</v>
       </c>
       <c r="H8">
-        <f t="shared" ref="H8:H18" si="7">2*SQRT(F8)/(1 + F8)</f>
+        <f t="shared" ref="H8:H18" si="8">2*SQRT(F8)/(1 + F8)</f>
         <v>0.57992226580752393</v>
       </c>
       <c r="I8">
-        <f t="shared" ref="I8:I18" si="8">G8/H8</f>
+        <f t="shared" ref="I8:I18" si="9">G8/H8</f>
         <v>0.39516790469763929</v>
       </c>
       <c r="K8">
         <f t="shared" si="4"/>
         <v>0.17863182637569197</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L8">
+        <f t="shared" si="5"/>
+        <v>0.42264858496828306</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>60</v>
       </c>
@@ -2679,27 +2866,31 @@
         <v>31</v>
       </c>
       <c r="F9">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.10204081632653061</v>
       </c>
       <c r="G9">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.27835051546391754</v>
       </c>
       <c r="H9">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.57972132749994554</v>
       </c>
       <c r="I9">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.48014537720098571</v>
       </c>
       <c r="K9">
         <f t="shared" si="4"/>
         <v>0.25002674726441443</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L9">
+        <f t="shared" si="5"/>
+        <v>0.50002674654903656</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>55</v>
       </c>
@@ -2716,27 +2907,31 @@
         <v>38</v>
       </c>
       <c r="F10">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.12</v>
       </c>
       <c r="G10">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.40740740740740738</v>
       </c>
       <c r="H10">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.61858957413174187</v>
       </c>
       <c r="I10">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.65860697374223975</v>
       </c>
       <c r="K10">
         <f t="shared" si="4"/>
         <v>0.32901653207908127</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L10">
+        <f t="shared" si="5"/>
+        <v>0.57359962698652556</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>50</v>
       </c>
@@ -2753,27 +2948,31 @@
         <v>17</v>
       </c>
       <c r="F11">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
       <c r="G11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.47826086956521741</v>
       </c>
       <c r="H11">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.67356232107955083</v>
       </c>
       <c r="I11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.71004694680469305</v>
       </c>
       <c r="K11">
         <f t="shared" si="4"/>
         <v>0.41320125738531804</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L11">
+        <f t="shared" si="5"/>
+        <v>0.6428073252424229</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>45</v>
       </c>
@@ -2790,27 +2989,31 @@
         <v>17.5</v>
       </c>
       <c r="F12">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.15789473684210525</v>
       </c>
       <c r="G12">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.55555555555555558</v>
       </c>
       <c r="H12">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.6863485850246136</v>
       </c>
       <c r="I12">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.80943644042863794</v>
       </c>
       <c r="K12">
         <f t="shared" si="4"/>
         <v>0.50002316339744002</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L12">
+        <f t="shared" si="5"/>
+        <v>0.7071231599922605</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>40</v>
       </c>
@@ -2827,27 +3030,31 @@
         <v>17.5</v>
       </c>
       <c r="F13">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.15</v>
       </c>
       <c r="G13">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.55555555555555558</v>
       </c>
       <c r="H13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.67356232107955083</v>
       </c>
       <c r="I13">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.82480200891454247</v>
       </c>
       <c r="K13">
         <f t="shared" si="4"/>
         <v>0.58684436564286002</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L13">
+        <f t="shared" si="5"/>
+        <v>0.76605767775204758</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>35</v>
       </c>
@@ -2864,27 +3071,31 @@
         <v>20</v>
       </c>
       <c r="F14">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25</v>
       </c>
       <c r="G14">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="H14">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.8</v>
       </c>
       <c r="I14">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.83333333333333326</v>
       </c>
       <c r="K14">
         <f t="shared" si="4"/>
         <v>0.6710270010313284</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L14">
+        <f t="shared" si="5"/>
+        <v>0.81916237769524569</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>30</v>
       </c>
@@ -2901,27 +3112,31 @@
         <v>20.5</v>
       </c>
       <c r="F15">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.26315789473684209</v>
       </c>
       <c r="G15">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.67346938775510201</v>
       </c>
       <c r="H15">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.81223286206741363</v>
       </c>
       <c r="I15">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.82915801515453269</v>
       </c>
       <c r="K15">
         <f t="shared" si="4"/>
         <v>0.75001337327451822</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L15">
+        <f t="shared" si="5"/>
+        <v>0.86603312481366335</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>25</v>
       </c>
@@ -2938,27 +3153,31 @@
         <v>22.5</v>
       </c>
       <c r="F16">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3</v>
       </c>
       <c r="G16">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.76470588235294112</v>
       </c>
       <c r="H16">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.84265008846948619</v>
       </c>
       <c r="I16">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.90750110018012831</v>
       </c>
       <c r="K16">
         <f t="shared" si="4"/>
         <v>0.82140366262121145</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L16">
+        <f t="shared" si="5"/>
+        <v>0.90631322544758852</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>20</v>
       </c>
@@ -2975,27 +3194,31 @@
         <v>23.5</v>
       </c>
       <c r="F17">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.35</v>
       </c>
       <c r="G17">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.77358490566037741</v>
       </c>
       <c r="H17">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.87645626416290601</v>
       </c>
       <c r="I17">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.88262807545704525</v>
       </c>
       <c r="K17">
         <f t="shared" si="4"/>
         <v>0.8830288388760239</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L17">
+        <f t="shared" si="5"/>
+        <v>0.9396961417798968</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>10</v>
       </c>
@@ -3012,27 +3235,31 @@
         <v>26.5</v>
       </c>
       <c r="F18">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.5</v>
       </c>
       <c r="G18">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.82758620689655171</v>
       </c>
       <c r="H18">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.94280904158206347</v>
       </c>
       <c r="I18">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0.87778772836950714</v>
       </c>
       <c r="K18">
         <f t="shared" si="4"/>
         <v>0.96984807088994851</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L18">
+        <f t="shared" si="5"/>
+        <v>0.98480864683955149</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19" s="1">
         <v>100</v>
       </c>
@@ -3068,8 +3295,12 @@
         <f t="shared" si="4"/>
         <v>3.0136086877959174E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="L19">
+        <f>ABS(COS(A19/180 * 3.1415))</f>
+        <v>0.17359748522936377</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20" s="1">
         <v>95</v>
       </c>
@@ -3086,109 +3317,117 @@
         <v>27</v>
       </c>
       <c r="F20">
-        <f t="shared" ref="F20:F25" si="9">B20/C20</f>
+        <f t="shared" ref="F20:F25" si="10">B20/C20</f>
         <v>4.0816326530612242E-2</v>
       </c>
       <c r="G20">
-        <f t="shared" ref="G20:G25" si="10">(E20-D20)/(E20+D20)</f>
+        <f t="shared" ref="G20:G25" si="11">(E20-D20)/(E20+D20)</f>
         <v>5.8823529411764705E-2</v>
       </c>
       <c r="H20">
-        <f t="shared" ref="H20:H25" si="11">2*SQRT(F20)/(1 + F20)</f>
+        <f t="shared" ref="H20:H25" si="12">2*SQRT(F20)/(1 + F20)</f>
         <v>0.38821548771026132</v>
       </c>
       <c r="I20">
-        <f t="shared" ref="I20:I25" si="12">G20/H20</f>
+        <f t="shared" ref="I20:I25" si="13">G20/H20</f>
         <v>0.15152288168283162</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="K20">
+        <f t="shared" si="4"/>
+        <v>7.5876343651344012E-3</v>
+      </c>
+      <c r="L20">
+        <f>ABS(COS(A20/180 * 3.1415))</f>
+        <v>8.7107028218935359E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="F21" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G21" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H21" t="e">
+      <c r="G21" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I21" t="e">
+      <c r="H21" t="e">
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I21" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="F22" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G22" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H22" t="e">
+      <c r="G22" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I22" t="e">
+      <c r="H22" t="e">
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I22" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="F23" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G23" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H23" t="e">
+      <c r="G23" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I23" t="e">
+      <c r="H23" t="e">
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I23" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="F24" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G24" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H24" t="e">
+      <c r="G24" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="I24" t="e">
+      <c r="H24" t="e">
         <f t="shared" si="12"/>
         <v>#DIV/0!</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="I24" t="e">
+        <f t="shared" si="13"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="F25" t="e">
-        <f t="shared" si="9"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="G25" t="e">
         <f t="shared" si="10"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="H25" t="e">
+      <c r="G25" t="e">
         <f t="shared" si="11"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="H25" t="e">
+        <f t="shared" si="12"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="I25" t="e">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>#DIV/0!</v>
       </c>
     </row>
@@ -4126,7 +4365,8 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
